--- a/Result/profitability/4503.xlsx
+++ b/Result/profitability/4503.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1275000000000001</v>
+        <v>0.34875</v>
       </c>
       <c r="N2" t="n">
-        <v>12.3275</v>
+        <v>17.10875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1225</v>
+        <v>0.385</v>
       </c>
       <c r="N3" t="n">
-        <v>8.21875</v>
+        <v>14.77875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1325</v>
+        <v>0.31625</v>
       </c>
       <c r="N4" t="n">
-        <v>10.42625</v>
+        <v>14.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08000000000000004</v>
+        <v>0.2725</v>
       </c>
       <c r="N5" t="n">
-        <v>7.715</v>
+        <v>9.184999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07875000000000004</v>
+        <v>0.1525</v>
       </c>
       <c r="N6" t="n">
-        <v>6.571249999999999</v>
+        <v>7.84625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1175</v>
+        <v>-0.003749999999999976</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1812499999999995</v>
+        <v>4.141249999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.19375</v>
+        <v>-0.11125</v>
       </c>
       <c r="N8" t="n">
-        <v>1.516249999999999</v>
+        <v>2.05</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>181</v>
+      </c>
+      <c r="D75" t="n">
+        <v>108</v>
+      </c>
+      <c r="E75" t="n">
+        <v>74</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="G75" t="n">
+        <v>44</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>24.26%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>81</v>
+      </c>
+      <c r="J75" t="n">
+        <v>125</v>
+      </c>
+      <c r="K75" t="n">
+        <v>115</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.17625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8148148148148147</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.270000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1174367436743675</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4073432629026672</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
